--- a/Dados/Relatório de Posição 2026-07-10.xlsx
+++ b/Dados/Relatório de Posição 2026-07-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="847">
   <si>
     <t>Data</t>
   </si>
@@ -296,7 +296,7 @@
     <t>LFSN210099R</t>
   </si>
   <si>
-    <t>IPCA+ (2), CDI+ (1)</t>
+    <t>CDI+ (1), IPCA+ (2)</t>
   </si>
   <si>
     <t>19/11/2031</t>
@@ -818,7 +818,7 @@
     <t>DI1JUL28</t>
   </si>
   <si>
-    <t>Hedge IPCA (21)</t>
+    <t>Hedge DI (21), Hedge IPCA (21)</t>
   </si>
   <si>
     <t>03/07/2028</t>
@@ -845,7 +845,7 @@
     <t>DI1JUL27</t>
   </si>
   <si>
-    <t>Hedge IPCA (1)</t>
+    <t>Hedge IPCA (1), Hedge DI (1)</t>
   </si>
   <si>
     <t>01/07/2027</t>
@@ -866,7 +866,7 @@
     <t>DI1JAN27</t>
   </si>
   <si>
-    <t>Hedge DI (6), Pré (-33)</t>
+    <t>Pré (-33), Hedge DI (6)</t>
   </si>
   <si>
     <t>DAPMAI29</t>
@@ -905,7 +905,7 @@
     <t>03/01/2028</t>
   </si>
   <si>
-    <t>Pré (-36), Hedge DI (1)</t>
+    <t>Hedge DI (1), Pré (-36)</t>
   </si>
   <si>
     <t>DOLAGO26</t>
@@ -932,7 +932,10 @@
     <t>Hedge IPCA (-11)</t>
   </si>
   <si>
-    <t>Hedge DI (2), Risco (8)</t>
+    <t>Risco (8), Hedge DI (2)</t>
+  </si>
+  <si>
+    <t>Hedge DI (1), Hedge IPCA (1)</t>
   </si>
   <si>
     <t>DDIJAN27</t>
@@ -1526,7 +1529,7 @@
     <t>0.99y</t>
   </si>
   <si>
-    <t>CDI+ (26), IPCA+ (722)</t>
+    <t>IPCA+ (722), CDI+ (26)</t>
   </si>
   <si>
     <t>CDI+ (1.373)</t>
@@ -8906,7 +8909,7 @@
         <v>266</v>
       </c>
       <c r="F165" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="G165" t="s">
         <v>268</v>
@@ -8935,7 +8938,7 @@
         <v>35</v>
       </c>
       <c r="E166" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F166" t="s">
         <v>18</v>
@@ -8967,7 +8970,7 @@
         <v>280</v>
       </c>
       <c r="F167" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G167" t="s">
         <v>281</v>
@@ -8999,7 +9002,7 @@
         <v>284</v>
       </c>
       <c r="F168" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G168" t="s">
         <v>285</v>
@@ -9060,13 +9063,13 @@
         <v>35</v>
       </c>
       <c r="E170" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F170" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G170" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H170" t="s">
         <v>20</v>
@@ -9092,10 +9095,10 @@
         <v>35</v>
       </c>
       <c r="E171" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F171" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G171" t="s">
         <v>302</v>
@@ -9124,7 +9127,7 @@
         <v>35</v>
       </c>
       <c r="E172" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F172" t="s">
         <v>18</v>
@@ -9147,19 +9150,19 @@
         <v>13</v>
       </c>
       <c r="B173" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C173" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D173" t="s">
         <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F173" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H173" t="s">
         <v>20</v>
@@ -9182,19 +9185,19 @@
         <v>13</v>
       </c>
       <c r="B174" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C174" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D174" t="s">
         <v>34</v>
       </c>
       <c r="E174" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F174" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H174" t="s">
         <v>20</v>
@@ -9217,22 +9220,22 @@
         <v>13</v>
       </c>
       <c r="B175" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C175" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D175" t="s">
         <v>16</v>
       </c>
       <c r="E175" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F175" t="s">
         <v>18</v>
       </c>
       <c r="G175" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H175" t="s">
         <v>20</v>
@@ -9255,22 +9258,22 @@
         <v>13</v>
       </c>
       <c r="B176" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C176" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D176" t="s">
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F176" t="s">
         <v>18</v>
       </c>
       <c r="G176" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H176" t="s">
         <v>20</v>
@@ -9293,22 +9296,22 @@
         <v>13</v>
       </c>
       <c r="B177" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C177" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D177" t="s">
         <v>35</v>
       </c>
       <c r="E177" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F177" t="s">
         <v>18</v>
       </c>
       <c r="G177" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H177" t="s">
         <v>20</v>
@@ -9331,22 +9334,22 @@
         <v>13</v>
       </c>
       <c r="B178" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C178" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D178" t="s">
         <v>35</v>
       </c>
       <c r="E178" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F178" t="s">
         <v>18</v>
       </c>
       <c r="G178" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H178" t="s">
         <v>20</v>
@@ -9369,16 +9372,16 @@
         <v>13</v>
       </c>
       <c r="B179" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C179" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D179" t="s">
         <v>35</v>
       </c>
       <c r="E179" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F179" t="s">
         <v>18</v>
@@ -9404,16 +9407,16 @@
         <v>13</v>
       </c>
       <c r="B180" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D180" t="s">
         <v>35</v>
       </c>
       <c r="E180" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F180" t="s">
         <v>18</v>
@@ -9439,22 +9442,22 @@
         <v>13</v>
       </c>
       <c r="B181" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C181" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D181" t="s">
         <v>35</v>
       </c>
       <c r="E181" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F181" t="s">
         <v>18</v>
       </c>
       <c r="G181" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H181" t="s">
         <v>20</v>
@@ -9477,22 +9480,22 @@
         <v>13</v>
       </c>
       <c r="B182" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C182" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D182" t="s">
         <v>16</v>
       </c>
       <c r="E182" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
       </c>
       <c r="G182" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H182" t="s">
         <v>20</v>
@@ -9515,22 +9518,22 @@
         <v>13</v>
       </c>
       <c r="B183" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C183" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D183" t="s">
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F183" t="s">
         <v>18</v>
       </c>
       <c r="G183" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H183" t="s">
         <v>20</v>
@@ -9553,22 +9556,22 @@
         <v>13</v>
       </c>
       <c r="B184" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C184" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D184" t="s">
         <v>35</v>
       </c>
       <c r="E184" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F184" t="s">
         <v>18</v>
       </c>
       <c r="G184" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H184" t="s">
         <v>20</v>
@@ -9591,22 +9594,22 @@
         <v>13</v>
       </c>
       <c r="B185" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C185" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D185" t="s">
         <v>16</v>
       </c>
       <c r="E185" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F185" t="s">
         <v>18</v>
       </c>
       <c r="G185" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H185" t="s">
         <v>20</v>
@@ -9629,22 +9632,22 @@
         <v>13</v>
       </c>
       <c r="B186" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C186" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D186" t="s">
         <v>34</v>
       </c>
       <c r="E186" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F186" t="s">
         <v>18</v>
       </c>
       <c r="G186" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H186" t="s">
         <v>20</v>
@@ -9667,22 +9670,22 @@
         <v>13</v>
       </c>
       <c r="B187" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C187" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D187" t="s">
         <v>35</v>
       </c>
       <c r="E187" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F187" t="s">
         <v>18</v>
       </c>
       <c r="G187" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H187" t="s">
         <v>20</v>
@@ -9705,22 +9708,22 @@
         <v>13</v>
       </c>
       <c r="B188" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C188" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D188" t="s">
         <v>16</v>
       </c>
       <c r="E188" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F188" t="s">
         <v>18</v>
       </c>
       <c r="G188" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H188" t="s">
         <v>20</v>
@@ -9743,22 +9746,22 @@
         <v>13</v>
       </c>
       <c r="B189" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C189" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D189" t="s">
         <v>34</v>
       </c>
       <c r="E189" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F189" t="s">
         <v>18</v>
       </c>
       <c r="G189" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H189" t="s">
         <v>20</v>
@@ -9781,22 +9784,22 @@
         <v>13</v>
       </c>
       <c r="B190" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C190" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D190" t="s">
         <v>35</v>
       </c>
       <c r="E190" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F190" t="s">
         <v>18</v>
       </c>
       <c r="G190" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H190" t="s">
         <v>20</v>
@@ -9819,22 +9822,22 @@
         <v>13</v>
       </c>
       <c r="B191" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C191" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D191" t="s">
         <v>16</v>
       </c>
       <c r="E191" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F191" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G191" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H191" t="s">
         <v>20</v>
@@ -9857,22 +9860,22 @@
         <v>13</v>
       </c>
       <c r="B192" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C192" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D192" t="s">
         <v>34</v>
       </c>
       <c r="E192" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F192" t="s">
+        <v>348</v>
+      </c>
+      <c r="G192" t="s">
         <v>347</v>
-      </c>
-      <c r="G192" t="s">
-        <v>346</v>
       </c>
       <c r="H192" t="s">
         <v>20</v>
@@ -9895,22 +9898,22 @@
         <v>13</v>
       </c>
       <c r="B193" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C193" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D193" t="s">
         <v>35</v>
       </c>
       <c r="E193" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F193" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G193" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H193" t="s">
         <v>20</v>
@@ -9933,16 +9936,16 @@
         <v>13</v>
       </c>
       <c r="B194" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C194" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D194" t="s">
         <v>35</v>
       </c>
       <c r="E194" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F194" t="s">
         <v>18</v>
@@ -9971,22 +9974,22 @@
         <v>13</v>
       </c>
       <c r="B195" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C195" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D195" t="s">
         <v>35</v>
       </c>
       <c r="E195" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F195" t="s">
         <v>18</v>
       </c>
       <c r="G195" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H195" t="s">
         <v>20</v>
@@ -10009,22 +10012,22 @@
         <v>13</v>
       </c>
       <c r="B196" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C196" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D196" t="s">
         <v>16</v>
       </c>
       <c r="E196" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F196" t="s">
         <v>18</v>
       </c>
       <c r="G196" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H196" t="s">
         <v>20</v>
@@ -10047,22 +10050,22 @@
         <v>13</v>
       </c>
       <c r="B197" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C197" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D197" t="s">
         <v>34</v>
       </c>
       <c r="E197" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F197" t="s">
         <v>18</v>
       </c>
       <c r="G197" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H197" t="s">
         <v>20</v>
@@ -10085,22 +10088,22 @@
         <v>13</v>
       </c>
       <c r="B198" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C198" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D198" t="s">
         <v>35</v>
       </c>
       <c r="E198" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F198" t="s">
         <v>18</v>
       </c>
       <c r="G198" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H198" t="s">
         <v>20</v>
@@ -10123,16 +10126,16 @@
         <v>13</v>
       </c>
       <c r="B199" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C199" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D199" t="s">
         <v>35</v>
       </c>
       <c r="E199" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F199" t="s">
         <v>18</v>
@@ -10158,22 +10161,22 @@
         <v>13</v>
       </c>
       <c r="B200" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C200" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D200" t="s">
         <v>16</v>
       </c>
       <c r="E200" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F200" t="s">
         <v>18</v>
       </c>
       <c r="G200" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H200" t="s">
         <v>20</v>
@@ -10196,22 +10199,22 @@
         <v>13</v>
       </c>
       <c r="B201" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C201" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D201" t="s">
         <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F201" t="s">
         <v>18</v>
       </c>
       <c r="G201" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H201" t="s">
         <v>20</v>
@@ -10234,22 +10237,22 @@
         <v>13</v>
       </c>
       <c r="B202" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C202" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D202" t="s">
         <v>35</v>
       </c>
       <c r="E202" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F202" t="s">
         <v>18</v>
       </c>
       <c r="G202" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H202" t="s">
         <v>20</v>
@@ -10272,22 +10275,22 @@
         <v>13</v>
       </c>
       <c r="B203" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C203" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D203" t="s">
         <v>16</v>
       </c>
       <c r="E203" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F203" t="s">
         <v>18</v>
       </c>
       <c r="G203" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H203" t="s">
         <v>20</v>
@@ -10310,22 +10313,22 @@
         <v>13</v>
       </c>
       <c r="B204" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C204" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D204" t="s">
         <v>34</v>
       </c>
       <c r="E204" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F204" t="s">
         <v>18</v>
       </c>
       <c r="G204" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H204" t="s">
         <v>20</v>
@@ -10348,22 +10351,22 @@
         <v>13</v>
       </c>
       <c r="B205" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C205" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D205" t="s">
         <v>35</v>
       </c>
       <c r="E205" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F205" t="s">
         <v>18</v>
       </c>
       <c r="G205" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H205" t="s">
         <v>20</v>
@@ -10386,22 +10389,22 @@
         <v>13</v>
       </c>
       <c r="B206" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C206" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D206" t="s">
         <v>16</v>
       </c>
       <c r="E206" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F206" t="s">
         <v>18</v>
       </c>
       <c r="G206" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H206" t="s">
         <v>20</v>
@@ -10424,22 +10427,22 @@
         <v>13</v>
       </c>
       <c r="B207" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C207" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D207" t="s">
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F207" t="s">
         <v>18</v>
       </c>
       <c r="G207" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H207" t="s">
         <v>20</v>
@@ -10462,22 +10465,22 @@
         <v>13</v>
       </c>
       <c r="B208" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C208" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D208" t="s">
         <v>35</v>
       </c>
       <c r="E208" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F208" t="s">
         <v>18</v>
       </c>
       <c r="G208" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H208" t="s">
         <v>20</v>
@@ -10500,16 +10503,16 @@
         <v>13</v>
       </c>
       <c r="B209" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C209" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D209" t="s">
         <v>16</v>
       </c>
       <c r="E209" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F209" t="s">
         <v>18</v>
@@ -10535,16 +10538,16 @@
         <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C210" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D210" t="s">
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F210" t="s">
         <v>18</v>
@@ -10570,16 +10573,16 @@
         <v>13</v>
       </c>
       <c r="B211" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C211" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D211" t="s">
         <v>35</v>
       </c>
       <c r="E211" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F211" t="s">
         <v>18</v>
@@ -10605,22 +10608,22 @@
         <v>13</v>
       </c>
       <c r="B212" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C212" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D212" t="s">
         <v>16</v>
       </c>
       <c r="E212" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F212" t="s">
         <v>18</v>
       </c>
       <c r="G212" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H212" t="s">
         <v>20</v>
@@ -10643,22 +10646,22 @@
         <v>13</v>
       </c>
       <c r="B213" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C213" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D213" t="s">
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F213" t="s">
         <v>18</v>
       </c>
       <c r="G213" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H213" t="s">
         <v>20</v>
@@ -10681,22 +10684,22 @@
         <v>13</v>
       </c>
       <c r="B214" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C214" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D214" t="s">
         <v>35</v>
       </c>
       <c r="E214" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F214" t="s">
         <v>18</v>
       </c>
       <c r="G214" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H214" t="s">
         <v>20</v>
@@ -10719,22 +10722,22 @@
         <v>13</v>
       </c>
       <c r="B215" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C215" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D215" t="s">
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F215" t="s">
         <v>18</v>
       </c>
       <c r="G215" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H215" t="s">
         <v>20</v>
@@ -10757,22 +10760,22 @@
         <v>13</v>
       </c>
       <c r="B216" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C216" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D216" t="s">
         <v>16</v>
       </c>
       <c r="E216" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F216" t="s">
         <v>18</v>
       </c>
       <c r="G216" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H216" t="s">
         <v>20</v>
@@ -10795,22 +10798,22 @@
         <v>13</v>
       </c>
       <c r="B217" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C217" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D217" t="s">
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F217" t="s">
         <v>18</v>
       </c>
       <c r="G217" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H217" t="s">
         <v>20</v>
@@ -10833,16 +10836,16 @@
         <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C218" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D218" t="s">
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F218" t="s">
         <v>18</v>
@@ -10868,16 +10871,16 @@
         <v>13</v>
       </c>
       <c r="B219" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C219" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D219" t="s">
         <v>35</v>
       </c>
       <c r="E219" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F219" t="s">
         <v>18</v>
@@ -10903,22 +10906,22 @@
         <v>13</v>
       </c>
       <c r="B220" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C220" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D220" t="s">
         <v>16</v>
       </c>
       <c r="E220" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F220" t="s">
         <v>18</v>
       </c>
       <c r="G220" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H220" t="s">
         <v>20</v>
@@ -10941,22 +10944,22 @@
         <v>13</v>
       </c>
       <c r="B221" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C221" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D221" t="s">
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F221" t="s">
         <v>18</v>
       </c>
       <c r="G221" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H221" t="s">
         <v>20</v>
@@ -10979,22 +10982,22 @@
         <v>13</v>
       </c>
       <c r="B222" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C222" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D222" t="s">
         <v>35</v>
       </c>
       <c r="E222" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F222" t="s">
         <v>18</v>
       </c>
       <c r="G222" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H222" t="s">
         <v>20</v>
@@ -11017,25 +11020,25 @@
         <v>13</v>
       </c>
       <c r="B223" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C223" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D223" t="s">
         <v>16</v>
       </c>
       <c r="E223" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F223" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G223" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H223" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I223">
         <v>497.0</v>
@@ -11055,25 +11058,25 @@
         <v>13</v>
       </c>
       <c r="B224" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C224" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D224" t="s">
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F224" t="s">
+        <v>394</v>
+      </c>
+      <c r="G224" t="s">
+        <v>392</v>
+      </c>
+      <c r="H224" t="s">
         <v>393</v>
-      </c>
-      <c r="G224" t="s">
-        <v>391</v>
-      </c>
-      <c r="H224" t="s">
-        <v>392</v>
       </c>
       <c r="I224">
         <v>555.0</v>
@@ -11093,25 +11096,25 @@
         <v>13</v>
       </c>
       <c r="B225" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C225" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D225" t="s">
         <v>35</v>
       </c>
       <c r="E225" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F225" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G225" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H225" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I225">
         <v>490.0</v>
@@ -11131,22 +11134,22 @@
         <v>13</v>
       </c>
       <c r="B226" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C226" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D226" t="s">
         <v>16</v>
       </c>
       <c r="E226" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F226" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G226" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H226" t="s">
         <v>20</v>
@@ -11169,22 +11172,22 @@
         <v>13</v>
       </c>
       <c r="B227" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C227" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D227" t="s">
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F227" t="s">
+        <v>400</v>
+      </c>
+      <c r="G227" t="s">
         <v>399</v>
-      </c>
-      <c r="G227" t="s">
-        <v>398</v>
       </c>
       <c r="H227" t="s">
         <v>20</v>
@@ -11207,22 +11210,22 @@
         <v>13</v>
       </c>
       <c r="B228" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C228" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D228" t="s">
         <v>16</v>
       </c>
       <c r="E228" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F228" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G228" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H228" t="s">
         <v>20</v>
@@ -11245,22 +11248,22 @@
         <v>13</v>
       </c>
       <c r="B229" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C229" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D229" t="s">
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F229" t="s">
+        <v>404</v>
+      </c>
+      <c r="G229" t="s">
         <v>403</v>
-      </c>
-      <c r="G229" t="s">
-        <v>402</v>
       </c>
       <c r="H229" t="s">
         <v>20</v>
@@ -11283,22 +11286,22 @@
         <v>13</v>
       </c>
       <c r="B230" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C230" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D230" t="s">
         <v>35</v>
       </c>
       <c r="E230" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F230" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G230" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H230" t="s">
         <v>20</v>
@@ -11321,25 +11324,25 @@
         <v>13</v>
       </c>
       <c r="B231" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C231" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D231" t="s">
         <v>16</v>
       </c>
       <c r="E231" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F231" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G231" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H231" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I231">
         <v>2309.0</v>
@@ -11359,25 +11362,25 @@
         <v>13</v>
       </c>
       <c r="B232" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C232" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D232" t="s">
         <v>16</v>
       </c>
       <c r="E232" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F232" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G232" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H232" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I232">
         <v>1306.0</v>
@@ -11397,25 +11400,25 @@
         <v>13</v>
       </c>
       <c r="B233" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C233" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D233" t="s">
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F233" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G233" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H233" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I233">
         <v>1276.0</v>
@@ -11435,25 +11438,25 @@
         <v>13</v>
       </c>
       <c r="B234" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C234" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D234" t="s">
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F234" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G234" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H234" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I234">
         <v>1000.0</v>
@@ -11473,25 +11476,25 @@
         <v>13</v>
       </c>
       <c r="B235" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C235" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D235" t="s">
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F235" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G235" t="s">
         <v>195</v>
       </c>
       <c r="H235" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I235">
         <v>1340.0</v>
@@ -11511,25 +11514,25 @@
         <v>13</v>
       </c>
       <c r="B236" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C236" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D236" t="s">
         <v>16</v>
       </c>
       <c r="E236" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F236" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G236" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H236" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I236">
         <v>1838.0</v>
@@ -11549,25 +11552,25 @@
         <v>13</v>
       </c>
       <c r="B237" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C237" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D237" t="s">
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F237" t="s">
+        <v>425</v>
+      </c>
+      <c r="G237" t="s">
+        <v>423</v>
+      </c>
+      <c r="H237" t="s">
         <v>424</v>
-      </c>
-      <c r="G237" t="s">
-        <v>422</v>
-      </c>
-      <c r="H237" t="s">
-        <v>423</v>
       </c>
       <c r="I237">
         <v>1953.0</v>
@@ -11587,25 +11590,25 @@
         <v>13</v>
       </c>
       <c r="B238" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C238" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D238" t="s">
         <v>35</v>
       </c>
       <c r="E238" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F238" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G238" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H238" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I238">
         <v>3078.0</v>
@@ -11625,22 +11628,22 @@
         <v>13</v>
       </c>
       <c r="B239" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C239" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D239" t="s">
         <v>35</v>
       </c>
       <c r="E239" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F239" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G239" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H239" t="s">
         <v>20</v>
@@ -11663,22 +11666,22 @@
         <v>13</v>
       </c>
       <c r="B240" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C240" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D240" t="s">
         <v>16</v>
       </c>
       <c r="E240" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F240" t="s">
         <v>18</v>
       </c>
       <c r="G240" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H240" t="s">
         <v>20</v>
@@ -11701,22 +11704,22 @@
         <v>13</v>
       </c>
       <c r="B241" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C241" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D241" t="s">
         <v>16</v>
       </c>
       <c r="E241" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F241" t="s">
         <v>18</v>
       </c>
       <c r="G241" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H241" t="s">
         <v>20</v>
@@ -11739,22 +11742,22 @@
         <v>13</v>
       </c>
       <c r="B242" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C242" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D242" t="s">
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F242" t="s">
         <v>18</v>
       </c>
       <c r="G242" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H242" t="s">
         <v>20</v>
@@ -11777,22 +11780,22 @@
         <v>13</v>
       </c>
       <c r="B243" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C243" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D243" t="s">
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F243" t="s">
         <v>18</v>
       </c>
       <c r="G243" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H243" t="s">
         <v>20</v>
@@ -11815,25 +11818,25 @@
         <v>13</v>
       </c>
       <c r="B244" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C244" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D244" t="s">
         <v>35</v>
       </c>
       <c r="E244" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F244" t="s">
         <v>18</v>
       </c>
       <c r="G244" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H244" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I244">
         <v>1953.0</v>
@@ -11853,22 +11856,22 @@
         <v>13</v>
       </c>
       <c r="B245" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C245" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D245" t="s">
         <v>35</v>
       </c>
       <c r="E245" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F245" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G245" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H245" t="s">
         <v>20</v>
@@ -11891,25 +11894,25 @@
         <v>13</v>
       </c>
       <c r="B246" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C246" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D246" t="s">
         <v>16</v>
       </c>
       <c r="E246" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F246" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G246" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H246" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I246">
         <v>918.0</v>
@@ -11929,25 +11932,25 @@
         <v>13</v>
       </c>
       <c r="B247" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C247" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D247" t="s">
         <v>16</v>
       </c>
       <c r="E247" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F247" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G247" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H247" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I247">
         <v>5019.0</v>
@@ -11967,25 +11970,25 @@
         <v>13</v>
       </c>
       <c r="B248" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C248" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D248" t="s">
         <v>16</v>
       </c>
       <c r="E248" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F248" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G248" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H248" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I248">
         <v>1177.0</v>
@@ -12005,25 +12008,25 @@
         <v>13</v>
       </c>
       <c r="B249" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C249" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D249" t="s">
         <v>34</v>
       </c>
       <c r="E249" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F249" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G249" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H249" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I249">
         <v>2579.0</v>
@@ -12043,25 +12046,25 @@
         <v>13</v>
       </c>
       <c r="B250" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C250" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D250" t="s">
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F250" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G250" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H250" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I250">
         <v>81.0</v>
@@ -12081,25 +12084,25 @@
         <v>13</v>
       </c>
       <c r="B251" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C251" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D251" t="s">
         <v>35</v>
       </c>
       <c r="E251" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F251" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G251" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H251" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I251">
         <v>2547.0</v>
@@ -12119,25 +12122,25 @@
         <v>13</v>
       </c>
       <c r="B252" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C252" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D252" t="s">
         <v>35</v>
       </c>
       <c r="E252" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F252" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G252" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H252" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I252">
         <v>583.0</v>
@@ -12157,25 +12160,25 @@
         <v>13</v>
       </c>
       <c r="B253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C253" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D253" t="s">
         <v>16</v>
       </c>
       <c r="E253" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F253" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G253" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H253" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I253">
         <v>3240.0</v>
@@ -12195,25 +12198,25 @@
         <v>13</v>
       </c>
       <c r="B254" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C254" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D254" t="s">
         <v>16</v>
       </c>
       <c r="E254" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F254" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G254" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H254" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I254">
         <v>1416.0</v>
@@ -12233,25 +12236,25 @@
         <v>13</v>
       </c>
       <c r="B255" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C255" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D255" t="s">
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F255" t="s">
+        <v>471</v>
+      </c>
+      <c r="G255" t="s">
+        <v>469</v>
+      </c>
+      <c r="H255" t="s">
         <v>470</v>
-      </c>
-      <c r="G255" t="s">
-        <v>468</v>
-      </c>
-      <c r="H255" t="s">
-        <v>469</v>
       </c>
       <c r="I255">
         <v>1898.0</v>
@@ -12271,25 +12274,25 @@
         <v>13</v>
       </c>
       <c r="B256" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C256" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D256" t="s">
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F256" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G256" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H256" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I256">
         <v>1098.0</v>
@@ -12309,25 +12312,25 @@
         <v>13</v>
       </c>
       <c r="B257" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C257" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D257" t="s">
         <v>35</v>
       </c>
       <c r="E257" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F257" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G257" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H257" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I257">
         <v>2757.0</v>
@@ -12347,25 +12350,25 @@
         <v>13</v>
       </c>
       <c r="B258" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C258" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D258" t="s">
         <v>35</v>
       </c>
       <c r="E258" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F258" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G258" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H258" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I258">
         <v>564.0</v>
@@ -12385,25 +12388,25 @@
         <v>13</v>
       </c>
       <c r="B259" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C259" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D259" t="s">
         <v>16</v>
       </c>
       <c r="E259" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F259" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G259" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H259" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I259">
         <v>718.0</v>
@@ -12423,25 +12426,25 @@
         <v>13</v>
       </c>
       <c r="B260" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C260" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D260" t="s">
         <v>34</v>
       </c>
       <c r="E260" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F260" t="s">
+        <v>480</v>
+      </c>
+      <c r="G260" t="s">
+        <v>478</v>
+      </c>
+      <c r="H260" t="s">
         <v>479</v>
-      </c>
-      <c r="G260" t="s">
-        <v>477</v>
-      </c>
-      <c r="H260" t="s">
-        <v>478</v>
       </c>
       <c r="I260">
         <v>361.0</v>
@@ -12461,25 +12464,25 @@
         <v>13</v>
       </c>
       <c r="B261" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C261" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D261" t="s">
         <v>35</v>
       </c>
       <c r="E261" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F261" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G261" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H261" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I261">
         <v>1522.0</v>
@@ -12499,25 +12502,25 @@
         <v>13</v>
       </c>
       <c r="B262" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C262" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D262" t="s">
         <v>16</v>
       </c>
       <c r="E262" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F262" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G262" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H262" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I262">
         <v>2940.0</v>
@@ -12537,25 +12540,25 @@
         <v>13</v>
       </c>
       <c r="B263" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C263" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D263" t="s">
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F263" t="s">
+        <v>487</v>
+      </c>
+      <c r="G263" t="s">
+        <v>485</v>
+      </c>
+      <c r="H263" t="s">
         <v>486</v>
-      </c>
-      <c r="G263" t="s">
-        <v>484</v>
-      </c>
-      <c r="H263" t="s">
-        <v>485</v>
       </c>
       <c r="I263">
         <v>1796.0</v>
@@ -12575,25 +12578,25 @@
         <v>13</v>
       </c>
       <c r="B264" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C264" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D264" t="s">
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F264" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G264" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H264" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I264">
         <v>483.0</v>
@@ -12613,25 +12616,25 @@
         <v>13</v>
       </c>
       <c r="B265" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C265" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D265" t="s">
         <v>35</v>
       </c>
       <c r="E265" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F265" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G265" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H265" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I265">
         <v>1822.0</v>
@@ -12651,25 +12654,25 @@
         <v>13</v>
       </c>
       <c r="B266" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C266" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D266" t="s">
         <v>35</v>
       </c>
       <c r="E266" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F266" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G266" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H266" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I266">
         <v>1447.0</v>
@@ -12689,25 +12692,25 @@
         <v>13</v>
       </c>
       <c r="B267" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C267" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D267" t="s">
         <v>16</v>
       </c>
       <c r="E267" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F267" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G267" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H267" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I267">
         <v>3948.0</v>
@@ -12727,25 +12730,25 @@
         <v>13</v>
       </c>
       <c r="B268" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C268" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D268" t="s">
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F268" t="s">
+        <v>497</v>
+      </c>
+      <c r="G268" t="s">
+        <v>495</v>
+      </c>
+      <c r="H268" t="s">
         <v>496</v>
-      </c>
-      <c r="G268" t="s">
-        <v>494</v>
-      </c>
-      <c r="H268" t="s">
-        <v>495</v>
       </c>
       <c r="I268">
         <v>4745.0</v>
@@ -12765,25 +12768,25 @@
         <v>13</v>
       </c>
       <c r="B269" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C269" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D269" t="s">
         <v>35</v>
       </c>
       <c r="E269" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F269" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G269" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H269" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I269">
         <v>5747.0</v>
@@ -12803,25 +12806,25 @@
         <v>13</v>
       </c>
       <c r="B270" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C270" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D270" t="s">
         <v>16</v>
       </c>
       <c r="E270" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F270" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G270" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H270" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I270">
         <v>1397.0</v>
@@ -12841,25 +12844,25 @@
         <v>13</v>
       </c>
       <c r="B271" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C271" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D271" t="s">
         <v>34</v>
       </c>
       <c r="E271" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F271" t="s">
+        <v>504</v>
+      </c>
+      <c r="G271" t="s">
+        <v>502</v>
+      </c>
+      <c r="H271" t="s">
         <v>503</v>
-      </c>
-      <c r="G271" t="s">
-        <v>501</v>
-      </c>
-      <c r="H271" t="s">
-        <v>502</v>
       </c>
       <c r="I271">
         <v>748.0</v>
@@ -12879,25 +12882,25 @@
         <v>13</v>
       </c>
       <c r="B272" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C272" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D272" t="s">
         <v>35</v>
       </c>
       <c r="E272" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F272" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G272" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H272" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I272">
         <v>1373.0</v>
@@ -12917,25 +12920,25 @@
         <v>13</v>
       </c>
       <c r="B273" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C273" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D273" t="s">
         <v>35</v>
       </c>
       <c r="E273" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F273" t="s">
         <v>18</v>
       </c>
       <c r="G273" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H273" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I273">
         <v>840.0</v>
@@ -12955,22 +12958,22 @@
         <v>13</v>
       </c>
       <c r="B274" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C274" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D274" t="s">
         <v>16</v>
       </c>
       <c r="E274" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F274" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G274" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H274" t="s">
         <v>20</v>
@@ -12993,22 +12996,22 @@
         <v>13</v>
       </c>
       <c r="B275" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C275" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D275" t="s">
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F275" t="s">
+        <v>514</v>
+      </c>
+      <c r="G275" t="s">
         <v>513</v>
-      </c>
-      <c r="G275" t="s">
-        <v>512</v>
       </c>
       <c r="H275" t="s">
         <v>20</v>
@@ -13031,25 +13034,25 @@
         <v>13</v>
       </c>
       <c r="B276" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C276" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D276" t="s">
         <v>16</v>
       </c>
       <c r="E276" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F276" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G276" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H276" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I276">
         <v>2850.0</v>
@@ -13069,25 +13072,25 @@
         <v>13</v>
       </c>
       <c r="B277" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C277" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D277" t="s">
         <v>16</v>
       </c>
       <c r="E277" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F277" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G277" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H277" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I277">
         <v>471.0</v>
@@ -13107,25 +13110,25 @@
         <v>13</v>
       </c>
       <c r="B278" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C278" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D278" t="s">
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F278" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G278" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H278" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I278">
         <v>2491.0</v>
@@ -13145,25 +13148,25 @@
         <v>13</v>
       </c>
       <c r="B279" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C279" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D279" t="s">
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F279" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G279" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H279" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I279">
         <v>604.0</v>
@@ -13183,25 +13186,25 @@
         <v>13</v>
       </c>
       <c r="B280" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C280" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D280" t="s">
         <v>35</v>
       </c>
       <c r="E280" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F280" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G280" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H280" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I280">
         <v>3809.0</v>
@@ -13221,25 +13224,25 @@
         <v>13</v>
       </c>
       <c r="B281" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C281" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D281" t="s">
         <v>35</v>
       </c>
       <c r="E281" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F281" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G281" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H281" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I281">
         <v>572.0</v>
@@ -13259,25 +13262,25 @@
         <v>13</v>
       </c>
       <c r="B282" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C282" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D282" t="s">
         <v>16</v>
       </c>
       <c r="E282" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F282" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G282" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H282" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I282">
         <v>1640.0</v>
@@ -13297,25 +13300,25 @@
         <v>13</v>
       </c>
       <c r="B283" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C283" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D283" t="s">
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F283" t="s">
+        <v>536</v>
+      </c>
+      <c r="G283" t="s">
+        <v>534</v>
+      </c>
+      <c r="H283" t="s">
         <v>535</v>
-      </c>
-      <c r="G283" t="s">
-        <v>533</v>
-      </c>
-      <c r="H283" t="s">
-        <v>534</v>
       </c>
       <c r="I283">
         <v>1910.0</v>
@@ -13335,25 +13338,25 @@
         <v>13</v>
       </c>
       <c r="B284" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C284" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D284" t="s">
         <v>35</v>
       </c>
       <c r="E284" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F284" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G284" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H284" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I284">
         <v>2016.0</v>
@@ -13373,25 +13376,25 @@
         <v>13</v>
       </c>
       <c r="B285" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C285" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D285" t="s">
         <v>16</v>
       </c>
       <c r="E285" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F285" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G285" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H285" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I285">
         <v>6438.0</v>
@@ -13411,25 +13414,25 @@
         <v>13</v>
       </c>
       <c r="B286" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C286" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D286" t="s">
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F286" t="s">
+        <v>546</v>
+      </c>
+      <c r="G286" t="s">
+        <v>544</v>
+      </c>
+      <c r="H286" t="s">
         <v>545</v>
-      </c>
-      <c r="G286" t="s">
-        <v>543</v>
-      </c>
-      <c r="H286" t="s">
-        <v>544</v>
       </c>
       <c r="I286">
         <v>4605.0</v>
@@ -13449,25 +13452,25 @@
         <v>13</v>
       </c>
       <c r="B287" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C287" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D287" t="s">
         <v>16</v>
       </c>
       <c r="E287" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F287" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G287" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H287" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I287">
         <v>1547.0</v>
@@ -13487,25 +13490,25 @@
         <v>13</v>
       </c>
       <c r="B288" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C288" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D288" t="s">
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F288" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G288" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H288" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I288">
         <v>1670.0</v>
@@ -13525,25 +13528,25 @@
         <v>13</v>
       </c>
       <c r="B289" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C289" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D289" t="s">
         <v>35</v>
       </c>
       <c r="E289" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F289" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G289" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H289" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I289">
         <v>1469.0</v>
@@ -13563,25 +13566,25 @@
         <v>13</v>
       </c>
       <c r="B290" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C290" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D290" t="s">
         <v>16</v>
       </c>
       <c r="E290" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F290" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G290" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I290">
         <v>2364.0</v>
@@ -13601,25 +13604,25 @@
         <v>13</v>
       </c>
       <c r="B291" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C291" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D291" t="s">
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F291" t="s">
+        <v>557</v>
+      </c>
+      <c r="G291" t="s">
+        <v>555</v>
+      </c>
+      <c r="H291" t="s">
         <v>556</v>
-      </c>
-      <c r="G291" t="s">
-        <v>554</v>
-      </c>
-      <c r="H291" t="s">
-        <v>555</v>
       </c>
       <c r="I291">
         <v>1448.0</v>
@@ -13639,22 +13642,22 @@
         <v>13</v>
       </c>
       <c r="B292" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C292" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D292" t="s">
         <v>16</v>
       </c>
       <c r="E292" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F292" t="s">
         <v>18</v>
       </c>
       <c r="G292" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H292" t="s">
         <v>20</v>
@@ -13677,22 +13680,22 @@
         <v>13</v>
       </c>
       <c r="B293" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C293" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D293" t="s">
         <v>16</v>
       </c>
       <c r="E293" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F293" t="s">
         <v>18</v>
       </c>
       <c r="G293" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H293" t="s">
         <v>20</v>
@@ -13715,22 +13718,22 @@
         <v>13</v>
       </c>
       <c r="B294" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C294" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D294" t="s">
         <v>16</v>
       </c>
       <c r="E294" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F294" t="s">
         <v>18</v>
       </c>
       <c r="G294" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H294" t="s">
         <v>20</v>
@@ -13753,22 +13756,22 @@
         <v>13</v>
       </c>
       <c r="B295" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C295" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D295" t="s">
         <v>16</v>
       </c>
       <c r="E295" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F295" t="s">
         <v>18</v>
       </c>
       <c r="G295" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H295" t="s">
         <v>20</v>
@@ -13791,22 +13794,22 @@
         <v>13</v>
       </c>
       <c r="B296" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C296" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D296" t="s">
         <v>16</v>
       </c>
       <c r="E296" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F296" t="s">
         <v>18</v>
       </c>
       <c r="G296" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H296" t="s">
         <v>20</v>
@@ -13829,22 +13832,22 @@
         <v>13</v>
       </c>
       <c r="B297" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C297" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D297" t="s">
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F297" t="s">
         <v>18</v>
       </c>
       <c r="G297" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H297" t="s">
         <v>20</v>
@@ -13867,22 +13870,22 @@
         <v>13</v>
       </c>
       <c r="B298" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C298" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D298" t="s">
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F298" t="s">
         <v>18</v>
       </c>
       <c r="G298" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H298" t="s">
         <v>20</v>
@@ -13905,22 +13908,22 @@
         <v>13</v>
       </c>
       <c r="B299" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C299" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D299" t="s">
         <v>34</v>
       </c>
       <c r="E299" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F299" t="s">
         <v>18</v>
       </c>
       <c r="G299" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H299" t="s">
         <v>20</v>
@@ -13943,22 +13946,22 @@
         <v>13</v>
       </c>
       <c r="B300" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C300" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D300" t="s">
         <v>34</v>
       </c>
       <c r="E300" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F300" t="s">
         <v>18</v>
       </c>
       <c r="G300" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H300" t="s">
         <v>20</v>
@@ -13981,22 +13984,22 @@
         <v>13</v>
       </c>
       <c r="B301" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C301" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D301" t="s">
         <v>34</v>
       </c>
       <c r="E301" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F301" t="s">
         <v>18</v>
       </c>
       <c r="G301" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H301" t="s">
         <v>20</v>
@@ -14019,22 +14022,22 @@
         <v>13</v>
       </c>
       <c r="B302" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C302" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D302" t="s">
         <v>35</v>
       </c>
       <c r="E302" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F302" t="s">
         <v>18</v>
       </c>
       <c r="G302" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H302" t="s">
         <v>20</v>
@@ -14057,22 +14060,22 @@
         <v>13</v>
       </c>
       <c r="B303" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C303" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D303" t="s">
         <v>35</v>
       </c>
       <c r="E303" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F303" t="s">
         <v>18</v>
       </c>
       <c r="G303" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H303" t="s">
         <v>20</v>
@@ -14095,22 +14098,22 @@
         <v>13</v>
       </c>
       <c r="B304" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C304" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D304" t="s">
         <v>35</v>
       </c>
       <c r="E304" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F304" t="s">
         <v>18</v>
       </c>
       <c r="G304" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H304" t="s">
         <v>20</v>
@@ -14133,25 +14136,25 @@
         <v>13</v>
       </c>
       <c r="B305" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C305" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D305" t="s">
         <v>16</v>
       </c>
       <c r="E305" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F305" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G305" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H305" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I305">
         <v>210.0</v>
@@ -14171,25 +14174,25 @@
         <v>13</v>
       </c>
       <c r="B306" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C306" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D306" t="s">
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F306" t="s">
+        <v>572</v>
+      </c>
+      <c r="G306" t="s">
+        <v>570</v>
+      </c>
+      <c r="H306" t="s">
         <v>571</v>
-      </c>
-      <c r="G306" t="s">
-        <v>569</v>
-      </c>
-      <c r="H306" t="s">
-        <v>570</v>
       </c>
       <c r="I306">
         <v>296.0</v>
@@ -14209,25 +14212,25 @@
         <v>13</v>
       </c>
       <c r="B307" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C307" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D307" t="s">
         <v>35</v>
       </c>
       <c r="E307" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F307" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G307" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H307" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I307">
         <v>222.0</v>
@@ -14247,25 +14250,25 @@
         <v>13</v>
       </c>
       <c r="B308" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C308" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D308" t="s">
         <v>16</v>
       </c>
       <c r="E308" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F308" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G308" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H308" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I308">
         <v>7388.0</v>
@@ -14285,25 +14288,25 @@
         <v>13</v>
       </c>
       <c r="B309" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C309" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D309" t="s">
         <v>34</v>
       </c>
       <c r="E309" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F309" t="s">
+        <v>579</v>
+      </c>
+      <c r="G309" t="s">
+        <v>577</v>
+      </c>
+      <c r="H309" t="s">
         <v>578</v>
-      </c>
-      <c r="G309" t="s">
-        <v>576</v>
-      </c>
-      <c r="H309" t="s">
-        <v>577</v>
       </c>
       <c r="I309">
         <v>2458.0</v>
@@ -14323,25 +14326,25 @@
         <v>13</v>
       </c>
       <c r="B310" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C310" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D310" t="s">
         <v>16</v>
       </c>
       <c r="E310" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F310" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G310" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H310" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I310">
         <v>1252.0</v>
@@ -14361,25 +14364,25 @@
         <v>13</v>
       </c>
       <c r="B311" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C311" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D311" t="s">
         <v>34</v>
       </c>
       <c r="E311" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F311" t="s">
+        <v>585</v>
+      </c>
+      <c r="G311" t="s">
+        <v>583</v>
+      </c>
+      <c r="H311" t="s">
         <v>584</v>
-      </c>
-      <c r="G311" t="s">
-        <v>582</v>
-      </c>
-      <c r="H311" t="s">
-        <v>583</v>
       </c>
       <c r="I311">
         <v>1103.0</v>
@@ -14399,25 +14402,25 @@
         <v>13</v>
       </c>
       <c r="B312" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C312" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D312" t="s">
         <v>35</v>
       </c>
       <c r="E312" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F312" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G312" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H312" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I312">
         <v>1245.0</v>
@@ -14437,25 +14440,25 @@
         <v>13</v>
       </c>
       <c r="B313" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C313" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D313" t="s">
         <v>35</v>
       </c>
       <c r="E313" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F313" t="s">
         <v>18</v>
       </c>
       <c r="G313" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H313" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I313">
         <v>100.0</v>
@@ -14475,25 +14478,25 @@
         <v>13</v>
       </c>
       <c r="B314" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C314" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D314" t="s">
         <v>16</v>
       </c>
       <c r="E314" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F314" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G314" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H314" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I314">
         <v>2511.0</v>
@@ -14513,25 +14516,25 @@
         <v>13</v>
       </c>
       <c r="B315" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C315" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D315" t="s">
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F315" t="s">
+        <v>595</v>
+      </c>
+      <c r="G315" t="s">
+        <v>593</v>
+      </c>
+      <c r="H315" t="s">
         <v>594</v>
-      </c>
-      <c r="G315" t="s">
-        <v>592</v>
-      </c>
-      <c r="H315" t="s">
-        <v>593</v>
       </c>
       <c r="I315">
         <v>1884.0</v>
@@ -14551,25 +14554,25 @@
         <v>13</v>
       </c>
       <c r="B316" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C316" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D316" t="s">
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F316" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G316" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H316" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I316">
         <v>1020.0</v>
@@ -14589,25 +14592,25 @@
         <v>13</v>
       </c>
       <c r="B317" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C317" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D317" t="s">
         <v>35</v>
       </c>
       <c r="E317" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F317" t="s">
+        <v>601</v>
+      </c>
+      <c r="G317" t="s">
+        <v>599</v>
+      </c>
+      <c r="H317" t="s">
         <v>600</v>
-      </c>
-      <c r="G317" t="s">
-        <v>598</v>
-      </c>
-      <c r="H317" t="s">
-        <v>599</v>
       </c>
       <c r="I317">
         <v>2489.0</v>
@@ -14627,25 +14630,25 @@
         <v>13</v>
       </c>
       <c r="B318" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C318" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D318" t="s">
         <v>16</v>
       </c>
       <c r="E318" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F318" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G318" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H318" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I318">
         <v>447.0</v>
@@ -14665,25 +14668,25 @@
         <v>13</v>
       </c>
       <c r="B319" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C319" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D319" t="s">
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F319" t="s">
+        <v>607</v>
+      </c>
+      <c r="G319" t="s">
+        <v>605</v>
+      </c>
+      <c r="H319" t="s">
         <v>606</v>
-      </c>
-      <c r="G319" t="s">
-        <v>604</v>
-      </c>
-      <c r="H319" t="s">
-        <v>605</v>
       </c>
       <c r="I319">
         <v>701.0</v>
@@ -14703,25 +14706,25 @@
         <v>13</v>
       </c>
       <c r="B320" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C320" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D320" t="s">
         <v>35</v>
       </c>
       <c r="E320" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F320" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G320" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H320" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I320">
         <v>821.0</v>
@@ -14741,25 +14744,25 @@
         <v>13</v>
       </c>
       <c r="B321" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C321" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D321" t="s">
         <v>35</v>
       </c>
       <c r="E321" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F321" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G321" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H321" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I321">
         <v>3497.0</v>
@@ -14779,25 +14782,25 @@
         <v>13</v>
       </c>
       <c r="B322" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C322" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D322" t="s">
         <v>16</v>
       </c>
       <c r="E322" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F322" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G322" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H322" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I322">
         <v>2830.0</v>
@@ -14817,25 +14820,25 @@
         <v>13</v>
       </c>
       <c r="B323" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C323" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D323" t="s">
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F323" t="s">
+        <v>619</v>
+      </c>
+      <c r="G323" t="s">
+        <v>617</v>
+      </c>
+      <c r="H323" t="s">
         <v>618</v>
-      </c>
-      <c r="G323" t="s">
-        <v>616</v>
-      </c>
-      <c r="H323" t="s">
-        <v>617</v>
       </c>
       <c r="I323">
         <v>3715.0</v>
@@ -14855,25 +14858,25 @@
         <v>13</v>
       </c>
       <c r="B324" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C324" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D324" t="s">
         <v>16</v>
       </c>
       <c r="E324" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F324" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G324" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H324" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I324">
         <v>318.0</v>
@@ -14893,25 +14896,25 @@
         <v>13</v>
       </c>
       <c r="B325" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C325" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D325" t="s">
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F325" t="s">
+        <v>625</v>
+      </c>
+      <c r="G325" t="s">
+        <v>623</v>
+      </c>
+      <c r="H325" t="s">
         <v>624</v>
-      </c>
-      <c r="G325" t="s">
-        <v>622</v>
-      </c>
-      <c r="H325" t="s">
-        <v>623</v>
       </c>
       <c r="I325">
         <v>240.0</v>
@@ -14931,25 +14934,25 @@
         <v>13</v>
       </c>
       <c r="B326" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C326" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D326" t="s">
         <v>35</v>
       </c>
       <c r="E326" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F326" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G326" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H326" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I326">
         <v>641.0</v>
@@ -14969,25 +14972,25 @@
         <v>13</v>
       </c>
       <c r="B327" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C327" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D327" t="s">
         <v>16</v>
       </c>
       <c r="E327" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F327" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G327" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H327" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I327">
         <v>2299.0</v>
@@ -15007,25 +15010,25 @@
         <v>13</v>
       </c>
       <c r="B328" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C328" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D328" t="s">
         <v>16</v>
       </c>
       <c r="E328" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F328" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G328" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H328" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I328">
         <v>1453.0</v>
@@ -15045,25 +15048,25 @@
         <v>13</v>
       </c>
       <c r="B329" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C329" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D329" t="s">
         <v>34</v>
       </c>
       <c r="E329" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F329" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G329" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H329" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I329">
         <v>2787.0</v>
@@ -15083,25 +15086,25 @@
         <v>13</v>
       </c>
       <c r="B330" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C330" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D330" t="s">
         <v>34</v>
       </c>
       <c r="E330" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F330" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G330" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H330" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I330">
         <v>618.0</v>
@@ -15121,25 +15124,25 @@
         <v>13</v>
       </c>
       <c r="B331" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C331" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D331" t="s">
         <v>34</v>
       </c>
       <c r="E331" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F331" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G331" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H331" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I331">
         <v>455.0</v>
@@ -15159,25 +15162,25 @@
         <v>13</v>
       </c>
       <c r="B332" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C332" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D332" t="s">
         <v>35</v>
       </c>
       <c r="E332" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F332" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G332" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H332" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I332">
         <v>3770.0</v>
@@ -15197,25 +15200,25 @@
         <v>13</v>
       </c>
       <c r="B333" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C333" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D333" t="s">
         <v>35</v>
       </c>
       <c r="E333" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F333" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G333" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H333" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I333">
         <v>2567.0</v>
@@ -15235,25 +15238,25 @@
         <v>13</v>
       </c>
       <c r="B334" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C334" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D334" t="s">
         <v>16</v>
       </c>
       <c r="E334" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F334" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G334" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H334" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I334">
         <v>1293.0</v>
@@ -15273,25 +15276,25 @@
         <v>13</v>
       </c>
       <c r="B335" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C335" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D335" t="s">
         <v>34</v>
       </c>
       <c r="E335" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F335" t="s">
+        <v>650</v>
+      </c>
+      <c r="G335" t="s">
         <v>649</v>
       </c>
-      <c r="G335" t="s">
-        <v>648</v>
-      </c>
       <c r="H335" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I335">
         <v>1326.0</v>
@@ -15311,25 +15314,25 @@
         <v>13</v>
       </c>
       <c r="B336" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C336" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D336" t="s">
         <v>35</v>
       </c>
       <c r="E336" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F336" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G336" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H336" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I336">
         <v>2012.0</v>
@@ -15349,25 +15352,25 @@
         <v>13</v>
       </c>
       <c r="B337" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C337" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D337" t="s">
         <v>16</v>
       </c>
       <c r="E337" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F337" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G337" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H337" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I337">
         <v>2408.0</v>
@@ -15387,25 +15390,25 @@
         <v>13</v>
       </c>
       <c r="B338" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C338" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D338" t="s">
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F338" t="s">
+        <v>657</v>
+      </c>
+      <c r="G338" t="s">
+        <v>655</v>
+      </c>
+      <c r="H338" t="s">
         <v>656</v>
-      </c>
-      <c r="G338" t="s">
-        <v>654</v>
-      </c>
-      <c r="H338" t="s">
-        <v>655</v>
       </c>
       <c r="I338">
         <v>2548.0</v>
@@ -15425,25 +15428,25 @@
         <v>13</v>
       </c>
       <c r="B339" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C339" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D339" t="s">
         <v>35</v>
       </c>
       <c r="E339" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F339" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G339" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H339" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I339">
         <v>1819.0</v>
@@ -15463,25 +15466,25 @@
         <v>13</v>
       </c>
       <c r="B340" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C340" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D340" t="s">
         <v>35</v>
       </c>
       <c r="E340" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F340" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G340" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H340" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I340">
         <v>1504.0</v>
@@ -15501,22 +15504,22 @@
         <v>13</v>
       </c>
       <c r="B341" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C341" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D341" t="s">
         <v>35</v>
       </c>
       <c r="E341" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F341" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G341" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H341" t="s">
         <v>20</v>
@@ -15539,22 +15542,22 @@
         <v>13</v>
       </c>
       <c r="B342" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C342" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D342" t="s">
         <v>16</v>
       </c>
       <c r="E342" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F342" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G342" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H342" t="s">
         <v>20</v>
@@ -15577,22 +15580,22 @@
         <v>13</v>
       </c>
       <c r="B343" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C343" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D343" t="s">
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F343" t="s">
+        <v>670</v>
+      </c>
+      <c r="G343" t="s">
         <v>669</v>
-      </c>
-      <c r="G343" t="s">
-        <v>668</v>
       </c>
       <c r="H343" t="s">
         <v>20</v>
@@ -15615,25 +15618,25 @@
         <v>13</v>
       </c>
       <c r="B344" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C344" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D344" t="s">
         <v>16</v>
       </c>
       <c r="E344" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F344" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G344" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H344" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I344">
         <v>1383.0</v>
@@ -15653,25 +15656,25 @@
         <v>13</v>
       </c>
       <c r="B345" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C345" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D345" t="s">
         <v>34</v>
       </c>
       <c r="E345" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F345" t="s">
+        <v>676</v>
+      </c>
+      <c r="G345" t="s">
+        <v>674</v>
+      </c>
+      <c r="H345" t="s">
         <v>675</v>
-      </c>
-      <c r="G345" t="s">
-        <v>673</v>
-      </c>
-      <c r="H345" t="s">
-        <v>674</v>
       </c>
       <c r="I345">
         <v>1406.0</v>
@@ -15691,25 +15694,25 @@
         <v>13</v>
       </c>
       <c r="B346" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C346" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D346" t="s">
         <v>35</v>
       </c>
       <c r="E346" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F346" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G346" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H346" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I346">
         <v>2854.0</v>
@@ -15729,25 +15732,25 @@
         <v>13</v>
       </c>
       <c r="B347" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C347" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D347" t="s">
         <v>16</v>
       </c>
       <c r="E347" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F347" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G347" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H347" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I347">
         <v>507.0</v>
@@ -15767,25 +15770,25 @@
         <v>13</v>
       </c>
       <c r="B348" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C348" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D348" t="s">
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F348" t="s">
+        <v>686</v>
+      </c>
+      <c r="G348" t="s">
+        <v>413</v>
+      </c>
+      <c r="H348" t="s">
         <v>685</v>
-      </c>
-      <c r="G348" t="s">
-        <v>412</v>
-      </c>
-      <c r="H348" t="s">
-        <v>684</v>
       </c>
       <c r="I348">
         <v>456.0</v>
@@ -15805,25 +15808,25 @@
         <v>13</v>
       </c>
       <c r="B349" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C349" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D349" t="s">
         <v>35</v>
       </c>
       <c r="E349" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F349" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G349" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H349" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I349">
         <v>810.0</v>
@@ -15843,22 +15846,22 @@
         <v>13</v>
       </c>
       <c r="B350" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C350" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D350" t="s">
         <v>35</v>
       </c>
       <c r="E350" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F350" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G350" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H350" t="s">
         <v>20</v>
@@ -15881,25 +15884,25 @@
         <v>13</v>
       </c>
       <c r="B351" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C351" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D351" t="s">
         <v>16</v>
       </c>
       <c r="E351" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F351" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G351" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H351" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I351">
         <v>1020.0</v>
@@ -15919,22 +15922,22 @@
         <v>13</v>
       </c>
       <c r="B352" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C352" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D352" t="s">
         <v>16</v>
       </c>
       <c r="E352" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F352" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G352" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H352" t="s">
         <v>20</v>
@@ -15957,22 +15960,22 @@
         <v>13</v>
       </c>
       <c r="B353" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C353" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D353" t="s">
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F353" t="s">
+        <v>701</v>
+      </c>
+      <c r="G353" t="s">
         <v>700</v>
-      </c>
-      <c r="G353" t="s">
-        <v>699</v>
       </c>
       <c r="H353" t="s">
         <v>20</v>
@@ -15995,22 +15998,22 @@
         <v>13</v>
       </c>
       <c r="B354" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C354" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D354" t="s">
         <v>35</v>
       </c>
       <c r="E354" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F354" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G354" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H354" t="s">
         <v>20</v>
@@ -16033,25 +16036,25 @@
         <v>13</v>
       </c>
       <c r="B355" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C355" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D355" t="s">
         <v>35</v>
       </c>
       <c r="E355" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F355" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G355" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H355" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I355">
         <v>3535.0</v>
@@ -16071,25 +16074,25 @@
         <v>13</v>
       </c>
       <c r="B356" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C356" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D356" t="s">
         <v>16</v>
       </c>
       <c r="E356" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F356" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G356" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H356" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I356">
         <v>3499.0</v>
@@ -16109,25 +16112,25 @@
         <v>13</v>
       </c>
       <c r="B357" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C357" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D357" t="s">
         <v>16</v>
       </c>
       <c r="E357" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F357" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G357" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H357" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I357">
         <v>1065.0</v>
@@ -16147,25 +16150,25 @@
         <v>13</v>
       </c>
       <c r="B358" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C358" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D358" t="s">
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F358" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G358" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H358" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I358">
         <v>3532.0</v>
@@ -16185,25 +16188,25 @@
         <v>13</v>
       </c>
       <c r="B359" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C359" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D359" t="s">
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F359" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G359" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H359" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I359">
         <v>945.0</v>
@@ -16223,25 +16226,25 @@
         <v>13</v>
       </c>
       <c r="B360" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C360" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D360" t="s">
         <v>35</v>
       </c>
       <c r="E360" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F360" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G360" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H360" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I360">
         <v>5268.0</v>
@@ -16261,25 +16264,25 @@
         <v>13</v>
       </c>
       <c r="B361" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C361" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D361" t="s">
         <v>35</v>
       </c>
       <c r="E361" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F361" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G361" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H361" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I361">
         <v>1005.0</v>
@@ -16299,22 +16302,22 @@
         <v>13</v>
       </c>
       <c r="B362" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C362" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D362" t="s">
         <v>16</v>
       </c>
       <c r="E362" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F362" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G362" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H362" t="s">
         <v>20</v>
@@ -16337,22 +16340,22 @@
         <v>13</v>
       </c>
       <c r="B363" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C363" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D363" t="s">
         <v>34</v>
       </c>
       <c r="E363" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F363" t="s">
+        <v>725</v>
+      </c>
+      <c r="G363" t="s">
         <v>724</v>
-      </c>
-      <c r="G363" t="s">
-        <v>723</v>
       </c>
       <c r="H363" t="s">
         <v>20</v>
@@ -16375,22 +16378,22 @@
         <v>13</v>
       </c>
       <c r="B364" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C364" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D364" t="s">
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F364" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G364" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H364" t="s">
         <v>20</v>
@@ -16413,22 +16416,22 @@
         <v>13</v>
       </c>
       <c r="B365" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D365" t="s">
         <v>35</v>
       </c>
       <c r="E365" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F365" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G365" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H365" t="s">
         <v>20</v>
@@ -16451,22 +16454,22 @@
         <v>13</v>
       </c>
       <c r="B366" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C366" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D366" t="s">
         <v>35</v>
       </c>
       <c r="E366" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F366" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G366" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H366" t="s">
         <v>20</v>
@@ -16489,22 +16492,22 @@
         <v>13</v>
       </c>
       <c r="B367" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C367" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D367" t="s">
         <v>35</v>
       </c>
       <c r="E367" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F367" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G367" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H367" t="s">
         <v>20</v>
@@ -16527,22 +16530,22 @@
         <v>13</v>
       </c>
       <c r="B368" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C368" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D368" t="s">
         <v>16</v>
       </c>
       <c r="E368" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F368" t="s">
         <v>18</v>
       </c>
       <c r="G368" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H368" t="s">
         <v>20</v>
@@ -16565,22 +16568,22 @@
         <v>13</v>
       </c>
       <c r="B369" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C369" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D369" t="s">
         <v>34</v>
       </c>
       <c r="E369" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F369" t="s">
         <v>18</v>
       </c>
       <c r="G369" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H369" t="s">
         <v>20</v>
@@ -16603,22 +16606,22 @@
         <v>13</v>
       </c>
       <c r="B370" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C370" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D370" t="s">
         <v>35</v>
       </c>
       <c r="E370" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F370" t="s">
         <v>18</v>
       </c>
       <c r="G370" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H370" t="s">
         <v>20</v>
@@ -16641,22 +16644,22 @@
         <v>13</v>
       </c>
       <c r="B371" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C371" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D371" t="s">
         <v>35</v>
       </c>
       <c r="E371" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F371" t="s">
         <v>18</v>
       </c>
       <c r="G371" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H371" t="s">
         <v>20</v>
@@ -16679,22 +16682,22 @@
         <v>13</v>
       </c>
       <c r="B372" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C372" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D372" t="s">
         <v>35</v>
       </c>
       <c r="E372" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F372" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G372" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H372" t="s">
         <v>20</v>
@@ -16717,25 +16720,25 @@
         <v>13</v>
       </c>
       <c r="B373" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C373" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D373" t="s">
         <v>35</v>
       </c>
       <c r="E373" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F373" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G373" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H373" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I373">
         <v>3078.0</v>
@@ -16755,22 +16758,22 @@
         <v>13</v>
       </c>
       <c r="B374" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C374" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D374" t="s">
         <v>16</v>
       </c>
       <c r="E374" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F374" t="s">
         <v>259</v>
       </c>
       <c r="G374" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H374" t="s">
         <v>20</v>
@@ -16793,22 +16796,22 @@
         <v>13</v>
       </c>
       <c r="B375" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C375" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D375" t="s">
         <v>34</v>
       </c>
       <c r="E375" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F375" t="s">
+        <v>748</v>
+      </c>
+      <c r="G375" t="s">
         <v>747</v>
-      </c>
-      <c r="G375" t="s">
-        <v>746</v>
       </c>
       <c r="H375" t="s">
         <v>20</v>
@@ -16831,25 +16834,25 @@
         <v>13</v>
       </c>
       <c r="B376" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C376" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D376" t="s">
         <v>16</v>
       </c>
       <c r="E376" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F376" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G376" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H376" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I376">
         <v>5487.0</v>
@@ -16869,25 +16872,25 @@
         <v>13</v>
       </c>
       <c r="B377" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C377" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D377" t="s">
         <v>16</v>
       </c>
       <c r="E377" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F377" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G377" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H377" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I377">
         <v>820.0</v>
@@ -16907,25 +16910,25 @@
         <v>13</v>
       </c>
       <c r="B378" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C378" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D378" t="s">
         <v>34</v>
       </c>
       <c r="E378" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F378" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G378" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H378" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I378">
         <v>4438.0</v>
@@ -16945,25 +16948,25 @@
         <v>13</v>
       </c>
       <c r="B379" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C379" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D379" t="s">
         <v>34</v>
       </c>
       <c r="E379" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F379" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G379" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H379" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I379">
         <v>252.0</v>
@@ -16983,22 +16986,22 @@
         <v>13</v>
       </c>
       <c r="B380" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C380" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D380" t="s">
         <v>35</v>
       </c>
       <c r="E380" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F380" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G380" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H380" t="s">
         <v>20</v>
@@ -17021,22 +17024,22 @@
         <v>13</v>
       </c>
       <c r="B381" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C381" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D381" t="s">
         <v>35</v>
       </c>
       <c r="E381" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F381" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G381" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H381" t="s">
         <v>20</v>
@@ -17059,22 +17062,22 @@
         <v>13</v>
       </c>
       <c r="B382" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C382" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D382" t="s">
         <v>16</v>
       </c>
       <c r="E382" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F382" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G382" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H382" t="s">
         <v>20</v>
@@ -17097,22 +17100,22 @@
         <v>13</v>
       </c>
       <c r="B383" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C383" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D383" t="s">
         <v>34</v>
       </c>
       <c r="E383" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F383" t="s">
+        <v>773</v>
+      </c>
+      <c r="G383" t="s">
         <v>772</v>
-      </c>
-      <c r="G383" t="s">
-        <v>771</v>
       </c>
       <c r="H383" t="s">
         <v>20</v>
@@ -17135,22 +17138,22 @@
         <v>13</v>
       </c>
       <c r="B384" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C384" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D384" t="s">
         <v>35</v>
       </c>
       <c r="E384" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F384" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G384" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H384" t="s">
         <v>20</v>
@@ -17173,22 +17176,22 @@
         <v>13</v>
       </c>
       <c r="B385" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C385" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D385" t="s">
         <v>35</v>
       </c>
       <c r="E385" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F385" t="s">
         <v>18</v>
       </c>
       <c r="G385" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H385" t="s">
         <v>20</v>
@@ -17211,22 +17214,22 @@
         <v>13</v>
       </c>
       <c r="B386" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C386" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D386" t="s">
         <v>35</v>
       </c>
       <c r="E386" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F386" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G386" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H386" t="s">
         <v>20</v>
@@ -17249,22 +17252,22 @@
         <v>13</v>
       </c>
       <c r="B387" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C387" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D387" t="s">
         <v>35</v>
       </c>
       <c r="E387" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F387" t="s">
         <v>18</v>
       </c>
       <c r="G387" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H387" t="s">
         <v>20</v>
@@ -17287,22 +17290,22 @@
         <v>13</v>
       </c>
       <c r="B388" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C388" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D388" t="s">
         <v>35</v>
       </c>
       <c r="E388" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F388" t="s">
         <v>18</v>
       </c>
       <c r="G388" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H388" t="s">
         <v>20</v>
@@ -17325,22 +17328,22 @@
         <v>13</v>
       </c>
       <c r="B389" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C389" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D389" t="s">
         <v>35</v>
       </c>
       <c r="E389" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F389" t="s">
         <v>18</v>
       </c>
       <c r="G389" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H389" t="s">
         <v>20</v>
@@ -17363,22 +17366,22 @@
         <v>13</v>
       </c>
       <c r="B390" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C390" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D390" t="s">
         <v>35</v>
       </c>
       <c r="E390" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F390" t="s">
         <v>18</v>
       </c>
       <c r="G390" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H390" t="s">
         <v>20</v>
@@ -17401,22 +17404,22 @@
         <v>13</v>
       </c>
       <c r="B391" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C391" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D391" t="s">
         <v>35</v>
       </c>
       <c r="E391" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F391" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G391" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H391" t="s">
         <v>20</v>
@@ -17439,22 +17442,22 @@
         <v>13</v>
       </c>
       <c r="B392" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C392" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D392" t="s">
         <v>35</v>
       </c>
       <c r="E392" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F392" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G392" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H392" t="s">
         <v>20</v>
@@ -17477,19 +17480,19 @@
         <v>13</v>
       </c>
       <c r="B393" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C393" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D393" t="s">
         <v>35</v>
       </c>
       <c r="E393" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F393" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H393" t="s">
         <v>20</v>
@@ -17512,7 +17515,7 @@
         <v>13</v>
       </c>
       <c r="B394" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C394" t="s">
         <v>15</v>
@@ -17550,7 +17553,7 @@
         <v>13</v>
       </c>
       <c r="B395" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C395" t="s">
         <v>15</v>
@@ -17565,7 +17568,7 @@
         <v>18</v>
       </c>
       <c r="G395" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H395" t="s">
         <v>20</v>
@@ -17588,7 +17591,7 @@
         <v>13</v>
       </c>
       <c r="B396" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C396" t="s">
         <v>15</v>
@@ -17603,7 +17606,7 @@
         <v>18</v>
       </c>
       <c r="G396" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H396" t="s">
         <v>20</v>
@@ -17626,7 +17629,7 @@
         <v>13</v>
       </c>
       <c r="B397" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C397" t="s">
         <v>15</v>
@@ -17641,7 +17644,7 @@
         <v>18</v>
       </c>
       <c r="G397" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H397" t="s">
         <v>20</v>
@@ -17664,7 +17667,7 @@
         <v>13</v>
       </c>
       <c r="B398" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C398" t="s">
         <v>15</v>
@@ -17702,7 +17705,7 @@
         <v>13</v>
       </c>
       <c r="B399" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C399" t="s">
         <v>15</v>
@@ -17717,7 +17720,7 @@
         <v>18</v>
       </c>
       <c r="G399" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H399" t="s">
         <v>20</v>
@@ -17740,7 +17743,7 @@
         <v>13</v>
       </c>
       <c r="B400" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C400" t="s">
         <v>15</v>
@@ -17755,7 +17758,7 @@
         <v>18</v>
       </c>
       <c r="G400" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H400" t="s">
         <v>20</v>
@@ -17778,7 +17781,7 @@
         <v>13</v>
       </c>
       <c r="B401" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C401" t="s">
         <v>85</v>
@@ -17793,7 +17796,7 @@
         <v>18</v>
       </c>
       <c r="G401" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H401" t="s">
         <v>20</v>
@@ -17816,22 +17819,22 @@
         <v>13</v>
       </c>
       <c r="B402" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C402" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D402" t="s">
         <v>16</v>
       </c>
       <c r="E402" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F402" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G402" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H402" t="s">
         <v>20</v>
@@ -17854,22 +17857,22 @@
         <v>13</v>
       </c>
       <c r="B403" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C403" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D403" t="s">
         <v>34</v>
       </c>
       <c r="E403" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F403" t="s">
+        <v>807</v>
+      </c>
+      <c r="G403" t="s">
         <v>806</v>
-      </c>
-      <c r="G403" t="s">
-        <v>805</v>
       </c>
       <c r="H403" t="s">
         <v>20</v>
@@ -17892,22 +17895,22 @@
         <v>13</v>
       </c>
       <c r="B404" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C404" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D404" t="s">
         <v>16</v>
       </c>
       <c r="E404" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F404" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G404" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H404" t="s">
         <v>20</v>
@@ -17930,22 +17933,22 @@
         <v>13</v>
       </c>
       <c r="B405" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C405" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D405" t="s">
         <v>34</v>
       </c>
       <c r="E405" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F405" t="s">
+        <v>812</v>
+      </c>
+      <c r="G405" t="s">
         <v>811</v>
-      </c>
-      <c r="G405" t="s">
-        <v>810</v>
       </c>
       <c r="H405" t="s">
         <v>20</v>
@@ -17968,7 +17971,7 @@
         <v>13</v>
       </c>
       <c r="B406" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C406" t="s">
         <v>85</v>
@@ -17977,13 +17980,13 @@
         <v>16</v>
       </c>
       <c r="E406" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F406" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G406" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H406" t="s">
         <v>20</v>
@@ -18006,7 +18009,7 @@
         <v>13</v>
       </c>
       <c r="B407" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C407" t="s">
         <v>261</v>
@@ -18015,13 +18018,13 @@
         <v>16</v>
       </c>
       <c r="E407" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F407" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G407" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H407" t="s">
         <v>20</v>
@@ -18044,7 +18047,7 @@
         <v>13</v>
       </c>
       <c r="B408" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C408" t="s">
         <v>261</v>
@@ -18053,13 +18056,13 @@
         <v>34</v>
       </c>
       <c r="E408" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F408" t="s">
+        <v>819</v>
+      </c>
+      <c r="G408" t="s">
         <v>818</v>
-      </c>
-      <c r="G408" t="s">
-        <v>817</v>
       </c>
       <c r="H408" t="s">
         <v>20</v>
@@ -18082,7 +18085,7 @@
         <v>13</v>
       </c>
       <c r="B409" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C409" t="s">
         <v>20</v>
@@ -18091,7 +18094,7 @@
         <v>41</v>
       </c>
       <c r="E409" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F409" t="s">
         <v>18</v>
@@ -18111,7 +18114,7 @@
         <v>13</v>
       </c>
       <c r="B410" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C410" t="s">
         <v>20</v>
@@ -18120,7 +18123,7 @@
         <v>42</v>
       </c>
       <c r="E410" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F410" t="s">
         <v>18</v>
@@ -18140,7 +18143,7 @@
         <v>13</v>
       </c>
       <c r="B411" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C411" t="s">
         <v>20</v>
@@ -18149,7 +18152,7 @@
         <v>16</v>
       </c>
       <c r="E411" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F411" t="s">
         <v>18</v>
@@ -18169,7 +18172,7 @@
         <v>13</v>
       </c>
       <c r="B412" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C412" t="s">
         <v>20</v>
@@ -18178,7 +18181,7 @@
         <v>34</v>
       </c>
       <c r="E412" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F412" t="s">
         <v>18</v>
@@ -18198,7 +18201,7 @@
         <v>13</v>
       </c>
       <c r="B413" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C413" t="s">
         <v>20</v>
@@ -18207,7 +18210,7 @@
         <v>35</v>
       </c>
       <c r="E413" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F413" t="s">
         <v>18</v>
@@ -18227,7 +18230,7 @@
         <v>13</v>
       </c>
       <c r="B414" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C414" t="s">
         <v>20</v>
@@ -18236,7 +18239,7 @@
         <v>43</v>
       </c>
       <c r="E414" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F414" t="s">
         <v>18</v>
@@ -18256,7 +18259,7 @@
         <v>13</v>
       </c>
       <c r="B415" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C415" t="s">
         <v>20</v>
@@ -18265,7 +18268,7 @@
         <v>44</v>
       </c>
       <c r="E415" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F415" t="s">
         <v>18</v>
@@ -18285,16 +18288,16 @@
         <v>13</v>
       </c>
       <c r="B416" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C416" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D416" t="s">
         <v>42</v>
       </c>
       <c r="E416" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F416" t="s">
         <v>18</v>
@@ -18314,16 +18317,16 @@
         <v>13</v>
       </c>
       <c r="B417" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C417" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D417" t="s">
         <v>41</v>
       </c>
       <c r="E417" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F417" t="s">
         <v>18</v>
@@ -18349,16 +18352,16 @@
         <v>13</v>
       </c>
       <c r="B418" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C418" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D418" t="s">
         <v>42</v>
       </c>
       <c r="E418" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F418" t="s">
         <v>18</v>
@@ -18384,16 +18387,16 @@
         <v>13</v>
       </c>
       <c r="B419" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C419" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D419" t="s">
         <v>41</v>
       </c>
       <c r="E419" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F419" t="s">
         <v>18</v>
@@ -18419,16 +18422,16 @@
         <v>13</v>
       </c>
       <c r="B420" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C420" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D420" t="s">
         <v>41</v>
       </c>
       <c r="E420" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F420" t="s">
         <v>18</v>
@@ -18454,16 +18457,16 @@
         <v>13</v>
       </c>
       <c r="B421" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C421" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D421" t="s">
         <v>42</v>
       </c>
       <c r="E421" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F421" t="s">
         <v>18</v>
@@ -18489,16 +18492,16 @@
         <v>13</v>
       </c>
       <c r="B422" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C422" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D422" t="s">
         <v>41</v>
       </c>
       <c r="E422" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F422" t="s">
         <v>18</v>
@@ -18524,16 +18527,16 @@
         <v>13</v>
       </c>
       <c r="B423" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C423" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D423" t="s">
         <v>42</v>
       </c>
       <c r="E423" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F423" t="s">
         <v>18</v>
@@ -18559,16 +18562,16 @@
         <v>13</v>
       </c>
       <c r="B424" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C424" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D424" t="s">
         <v>41</v>
       </c>
       <c r="E424" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F424" t="s">
         <v>18</v>
@@ -18594,16 +18597,16 @@
         <v>13</v>
       </c>
       <c r="B425" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C425" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D425" t="s">
         <v>42</v>
       </c>
       <c r="E425" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F425" t="s">
         <v>18</v>
@@ -18629,16 +18632,16 @@
         <v>13</v>
       </c>
       <c r="B426" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C426" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D426" t="s">
         <v>44</v>
       </c>
       <c r="E426" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F426" t="s">
         <v>18</v>
@@ -18664,19 +18667,19 @@
         <v>13</v>
       </c>
       <c r="B427" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C427" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D427" t="s">
         <v>35</v>
       </c>
       <c r="E427" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F427" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H427" t="s">
         <v>20</v>
@@ -18699,7 +18702,7 @@
         <v>13</v>
       </c>
       <c r="B428" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C428" t="s">
         <v>46</v>
@@ -18708,10 +18711,10 @@
         <v>35</v>
       </c>
       <c r="E428" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F428" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H428" t="s">
         <v>20</v>
@@ -18734,16 +18737,16 @@
         <v>13</v>
       </c>
       <c r="B429" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C429" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D429" t="s">
         <v>41</v>
       </c>
       <c r="E429" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F429" t="s">
         <v>18</v>
@@ -18769,16 +18772,16 @@
         <v>13</v>
       </c>
       <c r="B430" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C430" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D430" t="s">
         <v>42</v>
       </c>
       <c r="E430" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F430" t="s">
         <v>18</v>
@@ -18804,16 +18807,16 @@
         <v>13</v>
       </c>
       <c r="B431" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C431" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D431" t="s">
         <v>41</v>
       </c>
       <c r="E431" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F431" t="s">
         <v>18</v>
@@ -18839,16 +18842,16 @@
         <v>13</v>
       </c>
       <c r="B432" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C432" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D432" t="s">
         <v>42</v>
       </c>
       <c r="E432" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F432" t="s">
         <v>18</v>
@@ -18874,16 +18877,16 @@
         <v>13</v>
       </c>
       <c r="B433" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C433" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D433" t="s">
         <v>41</v>
       </c>
       <c r="E433" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F433" t="s">
         <v>18</v>
@@ -18909,16 +18912,16 @@
         <v>13</v>
       </c>
       <c r="B434" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C434" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D434" t="s">
         <v>42</v>
       </c>
       <c r="E434" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F434" t="s">
         <v>18</v>
@@ -18944,16 +18947,16 @@
         <v>13</v>
       </c>
       <c r="B435" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C435" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D435" t="s">
         <v>43</v>
       </c>
       <c r="E435" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F435" t="s">
         <v>18</v>
@@ -18979,16 +18982,16 @@
         <v>13</v>
       </c>
       <c r="B436" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C436" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D436" t="s">
         <v>44</v>
       </c>
       <c r="E436" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F436" t="s">
         <v>18</v>
@@ -19014,16 +19017,16 @@
         <v>13</v>
       </c>
       <c r="B437" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C437" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D437" t="s">
         <v>35</v>
       </c>
       <c r="E437" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F437" t="s">
         <v>18</v>
@@ -19049,7 +19052,7 @@
         <v>13</v>
       </c>
       <c r="B438" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C438" t="s">
         <v>20</v>
@@ -19058,7 +19061,7 @@
         <v>35</v>
       </c>
       <c r="E438" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F438" t="s">
         <v>18</v>
@@ -19084,7 +19087,7 @@
         <v>13</v>
       </c>
       <c r="B439" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C439" t="s">
         <v>20</v>
@@ -19093,7 +19096,7 @@
         <v>35</v>
       </c>
       <c r="E439" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F439" t="s">
         <v>18</v>
